--- a/Perf/speedup/17int_time.xlsx
+++ b/Perf/speedup/17int_time.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0225BC19-108F-40F0-AD9D-0DAC6909EB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F7F98C-54B0-4A12-963C-FC189B90FF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>vm-small</t>
   </si>
@@ -76,6 +76,22 @@
   <si>
     <t>557</t>
   </si>
+  <si>
+    <t>Perf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Perf error %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin error %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -104,12 +120,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -139,11 +161,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -159,6 +182,1049 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>2017 INT</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Perf error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$4:$N$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>70.271306058448644</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71.402330343620818</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70.005508247212802</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69.69279961658259</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>68.688791816082357</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.240151895940869</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.186515284800663</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7C25-43EE-936E-A95ADD2E8908}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pin error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$4:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>70.271306058448644</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69.759121843709181</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.072091567570553</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>66.906518248650855</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67.722029887798172</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>68.346662475565978</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>68.643283737271631</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7C25-43EE-936E-A95ADD2E8908}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2028560976"/>
+        <c:axId val="2028561456"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2028560976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2028561456"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2028561456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2028560976"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>549728</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>27213</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CC8BA30-5437-D866-2A26-16215BFD4D19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,10 +1512,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,7 +1529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -496,15 +1562,15 @@
         <v>0.96065442111876498</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>3.7963207649999999</v>
+        <v>0.04</v>
       </c>
       <c r="C3">
-        <v>3.2776559669999998</v>
+        <v>0.02</v>
       </c>
       <c r="D3">
         <v>9.4179032999999995E-2</v>
@@ -514,22 +1580,34 @@
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F11" si="0">B3/C3</f>
-        <v>1.1582425987419076</v>
-      </c>
-      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G11" si="1">B3/D3</f>
-        <v>40.30961716287743</v>
-      </c>
-      <c r="H3">
+        <v>0.42472298478579623</v>
+      </c>
+      <c r="H3" s="2">
         <f t="shared" ref="H3:H11" si="2">B3/E3</f>
-        <v>33.596832891684997</v>
+        <v>0.35399361614992508</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I11" si="3">AVERAGE(F3:H3)</f>
-        <v>25.021564217768113</v>
+        <f>AVERAGE(F3:H3)</f>
+        <v>0.92623886697857361</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -558,11 +1636,30 @@
         <v>0.85493462855209135</v>
       </c>
       <c r="I4">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="I3:I11" si="3">AVERAGE(F4:H4)</f>
         <v>1.0326110120284675</v>
       </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <f>AVERAGE(I7,AVERAGE(I2:I6,I8:I11))</f>
+        <v>1.0361353590926474</v>
+      </c>
+      <c r="N4">
+        <f>100*ABS(M4-3.485304)/3.485304</f>
+        <v>70.271306058448644</v>
+      </c>
+      <c r="O4">
+        <f>AVERAGE(I7,AVERAGE(I2:I6,I8:I11))</f>
+        <v>1.0361353590926474</v>
+      </c>
+      <c r="P4">
+        <f>100*ABS(O4-3.485304)/3.485304</f>
+        <v>70.271306058448644</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -594,8 +1691,27 @@
         <f t="shared" si="3"/>
         <v>1.0663759885874418</v>
       </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <f>AVERAGE(I7,I4,AVERAGE(I2,I3,I5:I6,I8:I11,))</f>
+        <v>0.99671572444057011</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N10" si="4">100*ABS(M5-3.485304)/3.485304</f>
+        <v>71.402330343620818</v>
+      </c>
+      <c r="O5">
+        <f>AVERAGE(I7,AVERAGE(I8:I11),AVERAGE(I2:I6))</f>
+        <v>1.0539865360163301</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:P10" si="5">100*ABS(O5-3.485304)/3.485304</f>
+        <v>69.759121843709181</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -627,8 +1743,27 @@
         <f t="shared" si="3"/>
         <v>1.3623563204531903</v>
       </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <f>AVERAGE(I7,I4,I5,AVERAGE(I2,I3,I6,I8:I11))</f>
+        <v>1.0453992208395624</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="4"/>
+        <v>70.005508247212802</v>
+      </c>
+      <c r="O6">
+        <f>AVERAGE(I7,AVERAGE(I8:I11),AVERAGE(I2:I5),I6)</f>
+        <v>1.1127846697118011</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="5"/>
+        <v>68.072091567570553</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -660,8 +1795,27 @@
         <f t="shared" si="3"/>
         <v>0.98659014192768113</v>
       </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGE(I7,I4,I5,AVERAGE(I8:I10),AVERAGE(I2:I3,I6,I11))</f>
+        <v>1.0562980672512627</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="4"/>
+        <v>69.69279961658259</v>
+      </c>
+      <c r="O7">
+        <f>AVERAGE(I7,I10,I6,AVERAGE(I8,I9,I11),AVERAGE(I2:I5))</f>
+        <v>1.1534084432190415</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="5"/>
+        <v>66.906518248650855</v>
+      </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -693,8 +1847,27 @@
         <f t="shared" si="3"/>
         <v>0.94844081244279765</v>
       </c>
+      <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8">
+        <f>AVERAGE(I7,I4,I5,AVERAGE(I8:I9),I10,AVERAGE(I2:I3,I6,I11))</f>
+        <v>1.0912907912824088</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="4"/>
+        <v>68.688791816082357</v>
+      </c>
+      <c r="O8">
+        <f>AVERAGE(I7,I10,I9,AVERAGE(I8,I11),I6,AVERAGE(I2:I5))</f>
+        <v>1.1249853834393753</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="5"/>
+        <v>67.722029887798172</v>
+      </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -726,8 +1899,27 @@
         <f t="shared" si="3"/>
         <v>0.96510872127405545</v>
       </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9">
+        <f>AVERAGE(I7,I4,I5,I8,I9,I10,AVERAGE(I2:I3,I6,I11))</f>
+        <v>1.072074216364697</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="4"/>
+        <v>69.240151895940869</v>
+      </c>
+      <c r="O9">
+        <f>AVERAGE(I7,I10,I6,I2,AVERAGE(I8,I11),I9,AVERAGE(I3:I5))</f>
+        <v>1.1032150388725996</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="5"/>
+        <v>68.346662475565978</v>
+      </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -759,8 +1951,27 @@
         <f t="shared" si="3"/>
         <v>1.4209942337279948</v>
       </c>
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <f>AVERAGE(I7,I4,I5,I8,I9,I10,AVERAGE(I2:I3,I6),I11)</f>
+        <v>1.0739436153182313</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="4"/>
+        <v>69.186515284800663</v>
+      </c>
+      <c r="O10">
+        <f>AVERAGE(I7,I10,I9,I6,I2,I4,AVERAGE(I3,I5),AVERAGE(I8,I11))</f>
+        <v>1.0928768861735223</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="5"/>
+        <v>68.643283737271631</v>
+      </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -793,14 +2004,15 @@
         <v>1.0883448097072368</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I13">
         <f>AVERAGE(I2:I11)</f>
-        <v>3.4853040679035745</v>
+        <v>1.0757715328246207</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Perf/speedup/17int_time.xlsx
+++ b/Perf/speedup/17int_time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F7F98C-54B0-4A12-963C-FC189B90FF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC84970-191B-4761-A281-36AD629497D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1191,15 +1191,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>549728</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>495299</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>27213</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>538841</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1513,9 +1513,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>0.96065442111876498</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>0.85493462855209135</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I3:I11" si="3">AVERAGE(F4:H4)</f>
+        <f t="shared" ref="I4:I11" si="3">AVERAGE(F4:H4)</f>
         <v>1.0326110120284675</v>
       </c>
       <c r="L4">
@@ -1659,7 +1659,7 @@
         <v>70.271306058448644</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>69.759121843709181</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>68.072091567570553</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>66.906518248650855</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>67.722029887798172</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>68.346662475565978</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>68.643283737271631</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -2004,7 +2004,17 @@
         <v>1.0883448097072368</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="N12">
+        <f>AVERAGE(N4:N10)</f>
+        <v>69.783914751812674</v>
+      </c>
+      <c r="P12">
+        <f>AVERAGE(P4:P10)</f>
+        <v>68.531573402716432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="I13">
         <f>AVERAGE(I2:I11)</f>
         <v>1.0757715328246207</v>
